--- a/horizon excursion/35 years - bundles as antigen (ONGOING)/production_capacity_updated.xlsx
+++ b/horizon excursion/35 years - bundles as antigen (ONGOING)/production_capacity_updated.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/horizon excursion/35 years - bundles as antigen (ONGOING)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="206" documentId="13_ncr:1_{68782C53-48E3-42CA-912A-5E0671CC39DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A464C6C2-7F1F-462F-B25F-B21FBF903C6F}"/>
+  <xr:revisionPtr revIDLastSave="210" documentId="13_ncr:1_{68782C53-48E3-42CA-912A-5E0671CC39DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02955C6E-D9B6-457E-A284-717CD53AA161}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="2" xr2:uid="{752E71BE-3FD4-4CCA-ABF0-6C5710D300B4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{752E71BE-3FD4-4CCA-ABF0-6C5710D300B4}"/>
   </bookViews>
   <sheets>
     <sheet name="vaccine-producer list" sheetId="8" r:id="rId1"/>
@@ -1957,9 +1957,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1997,7 +1997,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2103,7 +2103,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2245,7 +2245,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -10255,11 +10255,11 @@
         <v>110</v>
       </c>
       <c r="C207" s="8">
-        <f t="shared" ref="C207:L207" si="0">SUM(C96+C136+C142)</f>
+        <f>SUM(C96+C136+C142)</f>
         <v>14777182.228013158</v>
       </c>
       <c r="D207" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C207:L207" si="0">SUM(D96+D136+D142)</f>
         <v>37949221.241086259</v>
       </c>
       <c r="E207" s="8">
@@ -10303,11 +10303,11 @@
         <v>110</v>
       </c>
       <c r="C208" s="8">
-        <f t="shared" ref="C208:L208" si="1">C138+C139</f>
+        <f>C138+C139</f>
         <v>331279149.4189564</v>
       </c>
       <c r="D208" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="C208:L208" si="1">D138+D139</f>
         <v>227385022.03396031</v>
       </c>
       <c r="E208" s="8">
@@ -10351,11 +10351,11 @@
         <v>110</v>
       </c>
       <c r="C209" s="8">
-        <f t="shared" ref="C209:L209" si="2">C132+C133</f>
+        <f>C132+C133</f>
         <v>26052155.976207186</v>
       </c>
       <c r="D209" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="C209:L209" si="2">D132+D133</f>
         <v>26626398.679317039</v>
       </c>
       <c r="E209" s="8">
@@ -10783,11 +10783,11 @@
         <v>110</v>
       </c>
       <c r="C218" s="8">
-        <f t="shared" ref="C218:L218" si="11">C8+C9</f>
+        <f>C8+C9</f>
         <v>438402962.04456699</v>
       </c>
       <c r="D218" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="C218:L218" si="11">D8+D9</f>
         <v>470271315.11104214</v>
       </c>
       <c r="E218" s="8">
@@ -14270,12 +14270,40 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="52">
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="A187:A191"/>
+    <mergeCell ref="A192:A195"/>
+    <mergeCell ref="A196:A198"/>
+    <mergeCell ref="A199:A203"/>
+    <mergeCell ref="A164:A167"/>
+    <mergeCell ref="A168:A172"/>
+    <mergeCell ref="A173:A175"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="A182:A186"/>
+    <mergeCell ref="A161:A163"/>
+    <mergeCell ref="A120:A122"/>
+    <mergeCell ref="A123:A125"/>
+    <mergeCell ref="A126:A129"/>
+    <mergeCell ref="A130:A134"/>
+    <mergeCell ref="A135:A136"/>
+    <mergeCell ref="A137:A140"/>
+    <mergeCell ref="A142:A145"/>
+    <mergeCell ref="A146:A149"/>
+    <mergeCell ref="A150:A152"/>
+    <mergeCell ref="A153:A156"/>
+    <mergeCell ref="A157:A160"/>
+    <mergeCell ref="A114:A118"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="A90:A94"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A113"/>
     <mergeCell ref="A70:A74"/>
     <mergeCell ref="A31:A33"/>
     <mergeCell ref="A34:A36"/>
@@ -14288,40 +14316,12 @@
     <mergeCell ref="A58:A61"/>
     <mergeCell ref="A62:A64"/>
     <mergeCell ref="A65:A69"/>
-    <mergeCell ref="A114:A118"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="A90:A94"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="A161:A163"/>
-    <mergeCell ref="A120:A122"/>
-    <mergeCell ref="A123:A125"/>
-    <mergeCell ref="A126:A129"/>
-    <mergeCell ref="A130:A134"/>
-    <mergeCell ref="A135:A136"/>
-    <mergeCell ref="A137:A140"/>
-    <mergeCell ref="A142:A145"/>
-    <mergeCell ref="A146:A149"/>
-    <mergeCell ref="A150:A152"/>
-    <mergeCell ref="A153:A156"/>
-    <mergeCell ref="A157:A160"/>
-    <mergeCell ref="A187:A191"/>
-    <mergeCell ref="A192:A195"/>
-    <mergeCell ref="A196:A198"/>
-    <mergeCell ref="A199:A203"/>
-    <mergeCell ref="A164:A167"/>
-    <mergeCell ref="A168:A172"/>
-    <mergeCell ref="A173:A175"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="A179:A181"/>
-    <mergeCell ref="A182:A186"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
